--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.27930274169972</v>
+        <v>8.332886695526206</v>
       </c>
       <c r="D2" t="n">
-        <v>51.02533262288336</v>
+        <v>8.291616551218546</v>
       </c>
       <c r="E2" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F2" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.77891327171677</v>
+        <v>7.114073406653976</v>
       </c>
       <c r="D3" t="n">
-        <v>43.45760772167154</v>
+        <v>7.061861254771626</v>
       </c>
       <c r="E3" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F3" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.16889229222007</v>
+        <v>5.552444997485762</v>
       </c>
       <c r="D4" t="n">
-        <v>33.82980148714172</v>
+        <v>5.497342741660529</v>
       </c>
       <c r="E4" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F4" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.32106584017066</v>
+        <v>4.764673199027732</v>
       </c>
       <c r="D5" t="n">
-        <v>29.03595083165291</v>
+        <v>4.718342010143598</v>
       </c>
       <c r="E5" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F5" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.47570447796559</v>
+        <v>6.414801977669408</v>
       </c>
       <c r="D6" t="n">
-        <v>39.3893911268577</v>
+        <v>6.400776058114377</v>
       </c>
       <c r="E6" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F6" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.30839429881557</v>
+        <v>2.00011407355753</v>
       </c>
       <c r="D7" t="n">
-        <v>11.92895418465344</v>
+        <v>1.938455055006185</v>
       </c>
       <c r="E7" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F7" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.74084701507819</v>
+        <v>6.620387639950206</v>
       </c>
       <c r="D8" t="n">
-        <v>40.94070559771507</v>
+        <v>6.652864659628698</v>
       </c>
       <c r="E8" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F8" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.03090367061966</v>
+        <v>6.342521846475695</v>
       </c>
       <c r="D9" t="n">
-        <v>38.85860829335619</v>
+        <v>6.314523847670381</v>
       </c>
       <c r="E9" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F9" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>12.49928884168725</v>
+        <v>2.031134436774177</v>
       </c>
       <c r="D10" t="n">
-        <v>12.87745782790729</v>
+        <v>2.092586897034935</v>
       </c>
       <c r="E10" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F10" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.50935613953541</v>
+        <v>4.145270372674505</v>
       </c>
       <c r="D11" t="n">
-        <v>25.89407634822254</v>
+        <v>4.207787406586164</v>
       </c>
       <c r="E11" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F11" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>56.79688988513369</v>
+        <v>9.229494606334224</v>
       </c>
       <c r="D12" t="n">
-        <v>56.75971147409244</v>
+        <v>9.223453114540021</v>
       </c>
       <c r="E12" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F12" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.40655022853618</v>
+        <v>6.078564412137129</v>
       </c>
       <c r="D13" t="n">
-        <v>38.08946978971967</v>
+        <v>6.189538840829447</v>
       </c>
       <c r="E13" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F13" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.12336781760105</v>
+        <v>5.05754727036017</v>
       </c>
       <c r="D14" t="n">
-        <v>33.69309082196632</v>
+        <v>5.475127258569526</v>
       </c>
       <c r="E14" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F14" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.94233014313343</v>
+        <v>8.765628648259183</v>
       </c>
       <c r="D15" t="n">
-        <v>54.06495691100934</v>
+        <v>8.785555498039018</v>
       </c>
       <c r="E15" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F15" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.21219058304226</v>
+        <v>7.509480969744368</v>
       </c>
       <c r="D16" t="n">
-        <v>46.40643795826488</v>
+        <v>7.541046168218044</v>
       </c>
       <c r="E16" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F16" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>18.59587404100282</v>
+        <v>3.021829531662959</v>
       </c>
       <c r="D17" t="n">
-        <v>18.54036826917011</v>
+        <v>3.012809843740143</v>
       </c>
       <c r="E17" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F17" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>16.65667330206158</v>
+        <v>2.706709411585007</v>
       </c>
       <c r="D18" t="n">
-        <v>16.88429058275532</v>
+        <v>2.74369721969774</v>
       </c>
       <c r="E18" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F18" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>21.37294165546908</v>
+        <v>3.473103019013726</v>
       </c>
       <c r="D19" t="n">
-        <v>21.25605314279028</v>
+        <v>3.45410863570342</v>
       </c>
       <c r="E19" t="n">
-        <v>13.55136030626733</v>
+        <v>2.202096049768441</v>
       </c>
       <c r="F19" t="n">
-        <v>13.51841366029558</v>
+        <v>2.196742219798032</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
